--- a/MRCC_Updated.xlsx
+++ b/MRCC_Updated.xlsx
@@ -559,7 +559,7 @@
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>Number of CC Abilties</t>
+          <t>Number of CC Abilities</t>
         </is>
       </c>
     </row>

--- a/MRCC_Updated.xlsx
+++ b/MRCC_Updated.xlsx
@@ -434,7 +434,7 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>If Y, Which CC?</t>
+          <t>If Y, Which CC (Passive)?</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -444,7 +444,7 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>If Y, Which CC?.1</t>
+          <t>If Y, Which CC (Melee)?</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -459,7 +459,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>If Y, Which CC?.2</t>
+          <t>If Y, Which CC (Primary)?</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -474,7 +474,7 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>If Y, Which CC?.3</t>
+          <t>If Y, Which CC (Secondary)?</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
@@ -489,7 +489,7 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>If Y, What CC?</t>
+          <t>If Y, Which CC (A1)?</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
@@ -504,7 +504,7 @@
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>If Y, What CC?.1</t>
+          <t>If Y, Which CC (A2)?</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
@@ -519,7 +519,7 @@
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>If Y, What CC?.2</t>
+          <t>If Y, Which CC (A3)?</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>If Y, What CC?.3</t>
+          <t>If Y, Which CC (A4)?</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
@@ -549,7 +549,7 @@
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>If Y, What CC?.4</t>
+          <t>If Y, Which CC (Ult)?</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Displacement</t>
+          <t>Launched</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Knocked Pulled</t>
+          <t>Pulled</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">

--- a/MRCC_Updated.xlsx
+++ b/MRCC_Updated.xlsx
@@ -3080,7 +3080,7 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Y</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -3112,7 +3112,7 @@
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3832,7 +3832,7 @@
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
